--- a/AAII_Financials/Quarterly/NSRGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NSRGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="92">
   <si>
     <t>NSRGY</t>
   </si>
@@ -656,83 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -775,17 +781,23 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>26341500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>51572900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>25161900</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -831,14 +843,20 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>27871700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,14 +902,20 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>23701100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -911,8 +935,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -958,14 +984,20 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>914200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1017,8 +1049,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1064,14 +1102,20 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>1120200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1114,17 +1158,23 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1141,8 +1191,10 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1188,14 +1240,20 @@
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>44083600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1241,14 +1299,20 @@
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>7489300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1268,8 +1332,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1315,14 +1381,20 @@
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-491100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1368,14 +1440,20 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>8985100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1418,17 +1496,23 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1474,14 +1558,20 @@
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>6998200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1527,14 +1617,20 @@
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>1696100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1586,8 +1682,14 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1633,14 +1735,20 @@
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>5302100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1686,14 +1794,20 @@
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>5936900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1745,8 +1859,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1789,17 +1909,23 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1851,8 +1977,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1904,8 +2036,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1951,14 +2089,20 @@
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>491100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2004,14 +2148,20 @@
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>5936900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2063,8 +2213,14 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2110,72 +2266,84 @@
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>5936900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2195,8 +2363,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2216,485 +2386,541 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4394800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4427000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5774600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5742600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5849500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5262700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6131200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6577400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5414000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5393300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5719300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5266300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4097800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4018100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5960000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3196800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3220200</v>
+      </c>
+      <c r="F42" s="3">
         <v>2082100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2070500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1085200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>976300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2554700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2740600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1701500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1695000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1229100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1131800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>775500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>760400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1333400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13933200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14035300</v>
+      </c>
+      <c r="F43" s="3">
         <v>15062700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14979100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15081500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13568600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13888000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>14898600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14525900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>14470400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>14582100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>13427200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13725100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>13458000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13411300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16412100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>16532400</v>
+      </c>
+      <c r="F44" s="3">
         <v>16158600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>16068900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>18149600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>16329000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>14632900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>15697700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>14629400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>14573500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>14127300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>13008300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16532200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>16210500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>16242600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7600200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7656000</v>
+      </c>
+      <c r="F45" s="3">
         <v>634300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>630800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>808500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>727400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1025200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1099800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>627600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>625200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>368100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>339000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1082900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1061800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>377400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46506200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46847100</v>
+      </c>
+      <c r="F46" s="3">
         <v>40316500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>40092600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>42038000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37821100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>38831100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>41656900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37756500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37612100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>36644700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>33742300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>37230400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>36505900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>37918400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18953000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>19091900</v>
+      </c>
+      <c r="F47" s="3">
         <v>19846100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>19735900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>21547100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>19385700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>19837100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>21280700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>19069700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>18996700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>19042600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>17534400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>18198400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>17844200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>17602000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38404700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>38686200</v>
+      </c>
+      <c r="F48" s="3">
         <v>41048000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>40819900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>40012300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>35998600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>37195700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>39902500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>35873600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>35736400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>36181500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>33315800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>33323600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>32675200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>32596500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>51703000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>52082000</v>
+      </c>
+      <c r="F49" s="3">
         <v>55878700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>55568200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>56753600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>51060600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>55000100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>59002500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>55473000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>55260800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>55718100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>51305100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>55859000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>54772000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>55694500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2746,8 +2972,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2799,61 +3031,73 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2175700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2191700</v>
+      </c>
+      <c r="F52" s="3">
         <v>2069500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2058000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2021900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1819100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1720400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1845600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1416600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1411200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1296800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1194100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1315300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1289700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1255600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2905,61 +3149,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>158891100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>160055900</v>
+      </c>
+      <c r="F54" s="3">
         <v>160351900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>159461000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>163619100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>147206300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>153682500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>164866000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>150905900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>150328700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>150286200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>138383100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>147062100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>144200200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>146194900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2979,8 +3235,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3000,326 +3258,364 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23008700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>23177300</v>
+      </c>
+      <c r="F57" s="3">
         <v>20300100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>20187400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>24068300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>21653900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>18412500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>19752300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>21815000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>21731600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>16857500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>15522300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>20076900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19686200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>17085000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20229000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>20377300</v>
+      </c>
+      <c r="F58" s="3">
         <v>14636500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14555200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>23408100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>21060000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>13091200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>14043900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>12489400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>12441700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>11182100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10296400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>15411300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>15111400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>11779300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6346500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6393100</v>
+      </c>
+      <c r="F59" s="3">
         <v>7443100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7401700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4824700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4340700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7898000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8472700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3771400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3757000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7951900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>7322100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3843100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3768300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6927900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56052000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>56462900</v>
+      </c>
+      <c r="F60" s="3">
         <v>51319800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>51034600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>58877400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>52971300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>47300800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>50742900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>44188700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>44019700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>44039600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>40551600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>45043900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>44167300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>43232700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57549500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>57971400</v>
+      </c>
+      <c r="F61" s="3">
         <v>58321500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>57997400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>59083600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>53156900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>57049400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>61200900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>60810100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>60577600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>54420100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>50109900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>51196800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>50200500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>46957300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1680700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1693000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1639400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1630300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1858500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1672000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1782200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1911900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1980900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1973300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1959500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1804300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2745700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2692200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2637700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3371,8 +3667,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3424,8 +3726,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3477,61 +3785,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122376200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>123273300</v>
+      </c>
+      <c r="F66" s="3">
         <v>118662000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>118002700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>127094900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>114345800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>113190500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>121427500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>113578900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>113144500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>107074300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>98593800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>105912700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>103851500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>99916700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3551,8 +3871,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3604,8 +3926,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3657,8 +3985,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3710,8 +4044,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3763,61 +4103,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72790800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>73324400</v>
+      </c>
+      <c r="F72" s="3">
         <v>80145000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>79699800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>74665500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>67175700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>73233800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>78563100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>67558400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>67300000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>81064300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>74643800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>70972000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>69590800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>80712000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3869,8 +4221,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3922,8 +4280,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3975,61 +4339,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36175700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>36440900</v>
+      </c>
+      <c r="F76" s="3">
         <v>41377100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>41147300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>36246400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>32610400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>39635600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>42519900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>36563500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>36423700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>42445900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>39084100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>40373900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>39588200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>45402100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4081,66 +4457,78 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4186,14 +4574,20 @@
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>5936900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4213,61 +4607,69 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1009700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>908400</v>
+      </c>
+      <c r="F83" s="3">
         <v>827100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>887300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>846300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>843100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>842000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>775300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>837000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>820700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>800800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>754500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>805900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>835600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>820500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>1986900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4319,8 +4721,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4372,8 +4780,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4425,8 +4839,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4478,8 +4898,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4531,61 +4957,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3305100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3329300</v>
+      </c>
+      <c r="F89" s="3">
         <v>6956300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6917700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3063100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2755800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>5354900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5744600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3878300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3863400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6056600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>5576900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3207800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3145300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4310700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>4452400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4605,61 +5043,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1094700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1102700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1315300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1308000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1534700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1380700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1541600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1653800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1582500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1576400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1812800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1669200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1486800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1457900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1472400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4711,8 +5157,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4764,61 +5216,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1554500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1565900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1817900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1807800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-933000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-839400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2319100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2487800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2459900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2450500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2233200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2056300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1360500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1334100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2410600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>2890900</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4838,61 +5302,69 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>4935600</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>4971800</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>4934700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>4439700</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>4349000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>4332400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>4374400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>4289300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-8619600</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4944,8 +5416,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4997,8 +5475,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5050,163 +5534,187 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2380600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2398000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-5196400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-5167500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2404200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2163000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2567900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2754800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1506800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1501000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2964200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2729400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-2663000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2611200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1700100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-9324500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-295500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-265900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-85500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-91700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>115700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>115300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-184100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-169500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-207900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-203800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-120600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-113600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>64400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>66800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>139200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-612000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-616500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-35900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-35700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-569600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-512500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>382400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>410200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>27300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>675100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>621700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1023600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1003700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>79500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1842000</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
